--- a/r5-aist-trustworthyai-poc-pipeline/StructureDefinition-ai-privacy-metadata.xlsx
+++ b/r5-aist-trustworthyai-poc-pipeline/StructureDefinition-ai-privacy-metadata.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T09:07:35+00:00</t>
+    <t>2026-06-18T11:52:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2242,7 +2242,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>124</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>75</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>18</v>
